--- a/input/mapping/003. OCB_GOLD_TCKH_V_CDR_AMT_QUANG.xlsx
+++ b/input/mapping/003. OCB_GOLD_TCKH_V_CDR_AMT_QUANG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ZoneC_BOC\V_CDR_RATE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D915595C-0181-4AB0-A87B-1F10954F7D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{D915595C-0181-4AB0-A87B-1F10954F7D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DA25D7E-90D1-4A20-B374-FD6D8C4465EF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -130,17 +130,16 @@
     <t xml:space="preserve">V_CDR_AMT </t>
   </si>
   <si>
-    <t xml:space="preserve">
-USE CATALOG IDENTIFIER(:curated);
+    <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
 CREATE OR REPLACE VIEW v_cdr_amt AS
 SELECT
     A.DATA_DATE,
     A.AR_ID,
-    SUM(A.AMT_DEC)                      AS CDR_AMT_DEC,      -- tong AMT_FCY am
-    SUM(A.AMT_EQ_DEC)                   AS CDR_AMT_EQ_DEC,   -- tong AMT_LCY am
-    SUM(A.AMT_INCR)                     AS CDR_AMT_INCR,     -- tong AMT_FCY duong
-    SUM(A.AMT_EQ_INCR)                  AS CDR_AMT_EQ_INCR   -- tong AMT_LCY duong
+    COALESCE(SUM(A.AMT_DEC), 0)         AS CDR_AMT_DEC,      -- tong AMT_FCY am
+    COALESCE(SUM(A.AMT_EQ_DEC), 0)      AS CDR_AMT_EQ_DEC,   -- tong AMT_LCY am
+    COALESCE(SUM(A.AMT_INCR), 0)        AS CDR_AMT_INCR,     -- tong AMT_FCY duong
+    COALESCE(SUM(A.AMT_EQ_INCR), 0)     AS CDR_AMT_EQ_INCR   -- tong AMT_LCY duong
 FROM (
     SELECT
         DATA_DATE,
@@ -753,6 +752,30 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -774,34 +797,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -1188,15 +1187,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="30" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
     </row>
     <row r="2" spans="1:27" ht="6" customHeight="1"/>
     <row r="3" spans="1:27" ht="21.75" customHeight="1">
@@ -1215,65 +1214,65 @@
     </row>
     <row r="4" spans="1:27" ht="8.25" customHeight="1"/>
     <row r="5" spans="1:27" ht="21.75" customHeight="1">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="37" t="s">
         <v>7</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="28" t="s">
+      <c r="G5" s="36" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="21.75" customHeight="1">
-      <c r="A6" s="42"/>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
+      <c r="A6" s="43"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
       <c r="D6" s="44"/>
       <c r="E6" s="45"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="42"/>
+      <c r="G6" s="43"/>
     </row>
     <row r="7" spans="1:27" ht="8.25" customHeight="1">
-      <c r="A7" s="42"/>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
+      <c r="A7" s="43"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
       <c r="D7" s="44"/>
       <c r="E7" s="45"/>
     </row>
     <row r="8" spans="1:27" ht="21.75" customHeight="1">
-      <c r="A8" s="42"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
+      <c r="A8" s="43"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
       <c r="D8" s="44"/>
       <c r="E8" s="45"/>
       <c r="F8" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="28" t="s">
+      <c r="G8" s="36" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="21.75" customHeight="1">
-      <c r="A9" s="42"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
+      <c r="A9" s="43"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
       <c r="D9" s="44"/>
       <c r="E9" s="46"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="42"/>
+      <c r="G9" s="43"/>
     </row>
     <row r="10" spans="1:27" ht="8.25" customHeight="1"/>
     <row r="11" spans="1:27" ht="21.75" customHeight="1"/>
@@ -1374,10 +1373,10 @@
       <c r="A2" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="42" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1385,10 +1384,10 @@
       <c r="A3" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="42" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1420,26 +1419,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.45" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" spans="1:7" ht="15">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
     </row>
     <row r="3" spans="1:7" ht="15">
       <c r="A3" s="15" t="s">
@@ -1457,10 +1456,10 @@
       <c r="E3" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="36" t="s">
+      <c r="F3" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="37"/>
+      <c r="G3" s="29"/>
     </row>
     <row r="4" spans="1:7" ht="64.5" customHeight="1">
       <c r="A4" s="20">
@@ -1478,8 +1477,8 @@
       <c r="E4" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
     </row>
     <row r="5" spans="1:7" ht="55.5" customHeight="1">
       <c r="A5" s="16"/>
@@ -1487,8 +1486,8 @@
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
       <c r="E5" s="24"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
     </row>
     <row r="6" spans="1:7" ht="14.45" customHeight="1">
       <c r="A6" s="34" t="s">
@@ -1498,8 +1497,8 @@
       <c r="C6" s="34"/>
       <c r="D6" s="34"/>
       <c r="E6" s="34"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
     </row>
     <row r="7" spans="1:7" ht="14.45" customHeight="1">
       <c r="A7" s="15" t="s">
@@ -1674,24 +1673,25 @@
     <row r="15" spans="1:7" ht="15"/>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A6:G6"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1867,17 +1867,16 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13A4566F-D1EC-454F-8FAD-07C768EA4035}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD9487F4-93F9-482D-8DFB-B47FE5C6DD84}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1885,5 +1884,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD9487F4-93F9-482D-8DFB-B47FE5C6DD84}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13A4566F-D1EC-454F-8FAD-07C768EA4035}"/>
 </file>